--- a/reports/devops-jobs-israel-2026-W40.xlsx
+++ b/reports/devops-jobs-israel-2026-W40.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28T13:41:54</t>
+    <t xml:space="preserve">2026-09-29T12:39:38</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -120,6 +120,45 @@
     <t xml:space="preserve">Days Open</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Security, Argo CD, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988909101?gh_jid=4988909101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4988910101?gh_jid=4988910101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineering Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4983402101?gh_jid=4983402101</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevSecOps Engineer</t>
   </si>
   <si>
@@ -129,9 +168,6 @@
     <t xml:space="preserve">Tel Aviv</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
   </si>
   <si>
@@ -144,9 +180,6 @@
     <t xml:space="preserve">Senior DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
   </si>
   <si>
@@ -570,6 +603,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
   </si>
   <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">21936 - DevOps Engineer</t>
   </si>
   <si>
@@ -585,6 +627,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
   </si>
   <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
     <t xml:space="preserve">Play Perfect</t>
   </si>
   <si>
@@ -615,6 +663,12 @@
     <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4471287704</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
@@ -624,771 +678,774 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
   </si>
   <si>
-    <t xml:space="preserve">ARAN Software</t>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireArc Technologies .LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 4218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanox Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Avon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireArc Technologies .LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 4218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanox Vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps- Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-avon-at-pagaya-4472747108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conntour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer 4210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT System Administrator 243902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4471252854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conntour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer 4210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QualiGate</t>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-qualigate-4470836918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software and DevOps Engineer, DOCA Verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-and-devops-engineer-doca-verification-at-nvidia-4404233510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Cloud Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Deployment Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-deployment-engineer-at-jeen-ai-4471412751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -1408,9 +1465,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
     <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
@@ -1631,7 +1685,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -1639,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1647,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1709,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="10">
@@ -1727,7 +1781,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1735,7 +1789,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1754,20 +1808,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1775,7 +1829,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1783,7 +1837,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1791,7 +1845,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1799,7 +1853,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1818,15 +1872,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -1834,23 +1888,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -1858,7 +1912,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -1866,7 +1920,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -1874,7 +1928,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1882,7 +1936,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1890,7 +1944,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1898,7 +1952,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -1906,7 +1960,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1914,7 +1968,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1922,7 +1976,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1930,7 +1984,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1938,7 +1992,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1966,13 +2020,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2">
@@ -1980,13 +2034,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3">
         <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1995,88 +2049,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>36.9</v>
+        <v>35.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.8</v>
+        <v>32.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.8</v>
+        <v>20.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2142,30 +2196,30 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>34</v>
@@ -2174,13 +2228,13 @@
         <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
@@ -2189,15 +2243,15 @@
         <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>34</v>
@@ -2206,30 +2260,30 @@
         <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>47</v>
@@ -2238,10 +2292,10 @@
         <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>49</v>
@@ -2256,7 +2310,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -2264,112 +2318,112 @@
         <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6" s="3">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J7" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>66</v>
@@ -2384,7 +2438,7 @@
         <v>68</v>
       </c>
       <c r="J9" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2392,112 +2446,112 @@
         <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J10" s="3">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>82</v>
@@ -2512,7 +2566,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -2520,16 +2574,16 @@
         <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>86</v>
@@ -2544,7 +2598,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2552,16 +2606,16 @@
         <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>90</v>
@@ -2576,152 +2630,152 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J16" s="3">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J18" s="3">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J19" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>111</v>
@@ -2733,59 +2787,59 @@
         <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="J20" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>119</v>
@@ -2797,10 +2851,10 @@
         <v>120</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J22" s="3">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -2808,115 +2862,115 @@
         <v>121</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="J23" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J24" s="3">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="J25" s="3">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
@@ -2928,289 +2982,295 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J27" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J28" s="3">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>44</v>
+        <v>147</v>
       </c>
       <c r="J29" s="3">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="J30" s="3">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J31" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="J32" s="3">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="J34" s="3">
         <v>41</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J34" s="3">
-        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="J35" s="3">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -3218,286 +3278,286 @@
         <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J36" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>40</v>
+        <v>189</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J41" s="3">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="J42" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3507,57 +3567,57 @@
         <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="J45" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>48</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3570,264 +3630,264 @@
         <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="J48" s="3">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="J51" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>40</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="J55" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3837,7 +3897,7 @@
         <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="J56" s="3">
         <v>6</v>
@@ -3845,169 +3905,169 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="J57" s="3">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J60" s="3">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>35</v>
+        <v>255</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -4017,57 +4077,57 @@
         <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="J62" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="J63" s="3">
-        <v>18</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -4077,237 +4137,237 @@
         <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>273</v>
+        <v>180</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>274</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="J67" s="3">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>223</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="J71" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>93</v>
+        <v>280</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E72" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4317,157 +4377,157 @@
         <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>64</v>
+        <v>290</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J73" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="J75" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="J76" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>301</v>
+        <v>180</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J77" s="3">
         <v>0</v>
@@ -4475,49 +4535,49 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>35</v>
+        <v>255</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J78" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4527,10 +4587,10 @@
         <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -4538,16 +4598,16 @@
         <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>35</v>
+        <v>255</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -4557,431 +4617,431 @@
         <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="J80" s="3">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="J81" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J82" s="3">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>193</v>
+        <v>318</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>323</v>
+        <v>208</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>324</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="J84" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>48</v>
+        <v>326</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>274</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>333</v>
+        <v>209</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>274</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>192</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>336</v>
+        <v>254</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J88" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>340</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>345</v>
+        <v>186</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>168</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>347</v>
+        <v>75</v>
       </c>
       <c r="J91" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>168</v>
+        <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -4989,126 +5049,366 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>355</v>
+        <v>179</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>221</v>
+        <v>353</v>
       </c>
       <c r="J95" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>68</v>
+        <v>294</v>
       </c>
       <c r="J96" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>363</v>
+        <v>239</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J98" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J98" s="3">
-        <v>4</v>
+      <c r="B100" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J103" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J104" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J105" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J106" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J106"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5207,6 +5507,14 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5214,8 +5522,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5248,13 +5556,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5262,56 +5570,56 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>231</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>246</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>252</v>
+        <v>202</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5319,18 +5627,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>262</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5338,18 +5646,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5357,18 +5665,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5376,18 +5684,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>301</v>
+        <v>180</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5395,18 +5703,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5414,18 +5722,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>320</v>
+        <v>183</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5433,18 +5741,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>175</v>
+        <v>348</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5452,18 +5760,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5471,18 +5779,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>175</v>
+        <v>361</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5490,18 +5798,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5509,11 +5817,30 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>353</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5529,6 +5856,7 @@
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5542,47 +5870,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -5590,7 +5918,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>142</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5598,23 +5926,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5622,31 +5950,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5654,7 +5982,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5662,7 +5990,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5684,12 +6012,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -5697,15 +6025,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -5713,7 +6041,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5721,15 +6049,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5737,7 +6065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5745,7 +6073,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5753,15 +6081,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>246</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>223</v>
+        <v>141</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5769,7 +6097,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>291</v>
+        <v>183</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5777,7 +6105,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5785,23 +6113,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>137</v>
+        <v>305</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5815,23 +6143,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
@@ -5839,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3">
         <v>26.9</v>
@@ -5853,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -5867,7 +6195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3">
         <v>13.4</v>
@@ -5881,7 +6209,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -5895,7 +6223,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -5909,13 +6237,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -5923,13 +6251,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5937,13 +6265,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5951,13 +6279,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>236</v>
+        <v>141</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5965,13 +6293,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>246</v>
       </c>
       <c r="C11" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5979,13 +6307,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.0</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5993,13 +6321,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6007,13 +6335,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>149</v>
+        <v>275</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6021,10 +6349,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>223</v>
+        <v>305</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6035,13 +6363,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>332</v>
+        <v>155</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6061,43 +6389,43 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6116,36 +6444,36 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>274</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6153,15 +6481,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6188,10 +6516,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6203,10 +6531,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6223,31 +6551,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -6255,31 +6583,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4">
@@ -6287,31 +6615,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>266</v>
+        <v>421</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -6319,31 +6647,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -6351,31 +6679,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7">
@@ -6383,31 +6711,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>333</v>
+        <v>435</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -6415,31 +6743,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
@@ -6447,31 +6775,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -6479,31 +6807,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11">
@@ -6511,31 +6839,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -6543,31 +6871,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="F12" s="3">
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -6575,31 +6903,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -6607,31 +6935,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F14" s="3">
         <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
@@ -6639,31 +6967,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>301</v>
+        <v>474</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -6671,31 +6999,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17">
@@ -6703,31 +7031,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>463</v>
+        <v>275</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F17" s="3">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
@@ -6735,31 +7063,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F18" s="3">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19">
@@ -6767,31 +7095,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
@@ -6799,31 +7127,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F20" s="3">
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -6831,31 +7159,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W40.xlsx
+++ b/reports/devops-jobs-israel-2026-W40.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29T12:39:38</t>
+    <t xml:space="preserve">2026-09-30T12:25:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -276,1243 +276,1207 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QualityAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4471287704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE-DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanox Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Avon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VYBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conntour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Cloud Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4472141600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471984090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4468903264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QualityAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nayax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4471287704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireArc Technologies .LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 4218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanox Vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conntour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer 4210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT System Administrator 243902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4471252854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1685,7 +1649,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -1693,7 +1657,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1709,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1745,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1789,7 +1753,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1772,12 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -1821,7 +1785,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1829,23 +1793,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1853,7 +1817,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1872,47 +1836,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>501</v>
+        <v>378</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -1920,15 +1884,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>491</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1936,15 +1900,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>503</v>
+        <v>376</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1952,7 +1916,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -1960,7 +1924,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1968,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1976,7 +1940,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1984,7 +1948,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1992,7 +1956,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2020,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2">
@@ -2034,13 +1998,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2049,88 +2013,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>35.9</v>
+        <v>39.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.2</v>
+        <v>7.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.3</v>
+        <v>37.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2143,7 +2107,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2214,7 +2178,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2246,7 +2210,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2242,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2310,7 +2274,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2342,7 +2306,7 @@
         <v>55</v>
       </c>
       <c r="J6" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -2374,7 +2338,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -2406,7 +2370,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -2438,7 +2402,7 @@
         <v>68</v>
       </c>
       <c r="J9" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2470,7 +2434,7 @@
         <v>55</v>
       </c>
       <c r="J10" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2502,7 +2466,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2534,7 +2498,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -2566,12 +2530,12 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>81</v>
@@ -2586,24 +2550,24 @@
         <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="J14" s="3">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>81</v>
@@ -2618,24 +2582,24 @@
         <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="J15" s="3">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>81</v>
@@ -2662,7 +2626,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -2694,7 +2658,7 @@
         <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -2702,10 +2666,10 @@
         <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>48</v>
@@ -2714,30 +2678,30 @@
         <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J18" s="3">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>48</v>
@@ -2746,36 +2710,36 @@
         <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J19" s="3">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>111</v>
@@ -2787,91 +2751,91 @@
         <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="J20" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="J21" s="3">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="J22" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>122</v>
@@ -2883,10 +2847,10 @@
         <v>123</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="J23" s="3">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -2894,10 +2858,10 @@
         <v>124</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>48</v>
@@ -2906,30 +2870,30 @@
         <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>48</v>
@@ -2938,19 +2902,19 @@
         <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J25" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -2958,16 +2922,16 @@
         <v>132</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>134</v>
@@ -2982,15 +2946,15 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>48</v>
@@ -3002,7 +2966,7 @@
         <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
@@ -3014,50 +2978,50 @@
         <v>139</v>
       </c>
       <c r="J27" s="3">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J28" s="3">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>48</v>
@@ -3066,103 +3030,103 @@
         <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="J30" s="3">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="J31" s="3">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>161</v>
+        <v>48</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
@@ -3171,27 +3135,27 @@
         <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>167</v>
@@ -3203,53 +3167,51 @@
         <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J34" s="3">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>48</v>
@@ -3257,20 +3219,18 @@
       <c r="E35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>175</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="J35" s="3">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -3278,10 +3238,10 @@
         <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
@@ -3294,57 +3254,57 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>37</v>
@@ -3357,27 +3317,27 @@
         <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="J38" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3387,37 +3347,37 @@
         <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>191</v>
+        <v>40</v>
       </c>
       <c r="J39" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J40" s="3">
         <v>6</v>
@@ -3425,19 +3385,19 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="D41" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3447,54 +3407,54 @@
         <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="J41" s="3">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3507,7 +3467,7 @@
         <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3518,10 +3478,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>48</v>
@@ -3534,40 +3494,40 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J45" s="3">
         <v>6</v>
@@ -3575,43 +3535,43 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="J46" s="3">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
@@ -3624,24 +3584,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J47" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
@@ -3654,54 +3614,54 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -3714,24 +3674,24 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="J50" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -3744,114 +3704,114 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="J52" s="3">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J53" s="3">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="J54" s="3">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
@@ -3864,27 +3824,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3894,27 +3854,27 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>180</v>
+        <v>243</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3924,24 +3884,24 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J57" s="3">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>48</v>
@@ -3954,57 +3914,57 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>180</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="J59" s="3">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>37</v>
@@ -4014,84 +3974,84 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>252</v>
+        <v>40</v>
       </c>
       <c r="J60" s="3">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>186</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="J62" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
@@ -4104,13 +4064,13 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="J63" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4118,10 +4078,10 @@
         <v>52</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>48</v>
@@ -4134,27 +4094,27 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4164,27 +4124,27 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4194,54 +4154,54 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="J66" s="3">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>180</v>
+        <v>275</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="J67" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
@@ -4254,24 +4214,24 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>277</v>
+        <v>175</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>48</v>
@@ -4284,27 +4244,27 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4317,21 +4277,21 @@
         <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>48</v>
@@ -4339,89 +4299,91 @@
       <c r="E71" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>171</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>287</v>
+        <v>172</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="J72" s="3">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>294</v>
+        <v>183</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>295</v>
+        <v>96</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
@@ -4434,24 +4396,24 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="J74" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>48</v>
@@ -4464,27 +4426,27 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>104</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>180</v>
+        <v>243</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>42</v>
@@ -4494,24 +4456,24 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="C77" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
@@ -4524,13 +4486,13 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78">
@@ -4538,40 +4500,40 @@
         <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>232</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>307</v>
+        <v>91</v>
       </c>
       <c r="J78" s="3">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>48</v>
@@ -4584,27 +4546,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="J79" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4614,30 +4576,30 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="J80" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
@@ -4647,10 +4609,10 @@
         <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82">
@@ -4658,70 +4620,70 @@
         <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>314</v>
+        <v>193</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>316</v>
+        <v>238</v>
       </c>
       <c r="J82" s="3">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>52</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>208</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>48</v>
@@ -4734,60 +4696,62 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J84" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="J85" s="3">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>326</v>
+        <v>186</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
@@ -4797,21 +4761,21 @@
         <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>261</v>
+        <v>40</v>
       </c>
       <c r="J86" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>48</v>
@@ -4824,27 +4788,27 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>75</v>
+        <v>277</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>171</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4860,18 +4824,18 @@
         <v>333</v>
       </c>
       <c r="J88" s="3">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>52</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>334</v>
+        <v>171</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>48</v>
@@ -4887,10 +4851,10 @@
         <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4901,45 +4865,43 @@
         <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="I90" s="3" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="J90" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>186</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
@@ -4949,7 +4911,7 @@
         <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J91" s="3">
         <v>1</v>
@@ -4963,7 +4925,7 @@
         <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
@@ -4979,21 +4941,21 @@
         <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>46</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>48</v>
@@ -5001,9 +4963,7 @@
       <c r="E93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>346</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
@@ -5014,7 +4974,7 @@
         <v>75</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5022,13 +4982,13 @@
         <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D94" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -5041,7 +5001,7 @@
         <v>350</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -5052,13 +5012,13 @@
         <v>351</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>42</v>
@@ -5071,51 +5031,51 @@
         <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>353</v>
+        <v>226</v>
       </c>
       <c r="J95" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>48</v>
@@ -5128,70 +5088,70 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="J98" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E99" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="J99" s="3">
         <v>0</v>
@@ -5199,216 +5159,36 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="D100" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J102" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J103" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J104" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J105" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J106" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J100"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5509,12 +5289,6 @@
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5522,9 +5296,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="55" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5556,70 +5330,70 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>39</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>265</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5627,18 +5401,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>203</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>348</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5646,18 +5420,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>215</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5665,18 +5439,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>266</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>180</v>
+        <v>364</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5684,163 +5458,11 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B15" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>380</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5849,14 +5471,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5870,39 +5484,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="B5" s="3">
         <v>21</v>
@@ -5910,15 +5524,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>385</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>142</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5926,7 +5540,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5934,15 +5548,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5950,15 +5564,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -5966,7 +5580,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -5974,7 +5588,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5982,15 +5596,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6003,7 +5617,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6012,28 +5626,28 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6049,7 +5663,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -6073,7 +5687,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6081,7 +5695,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -6089,7 +5703,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6097,7 +5711,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6105,7 +5719,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6113,7 +5727,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6121,15 +5735,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -6150,16 +5764,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -6167,13 +5781,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6181,10 +5795,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>23.8</v>
+        <v>18.6</v>
       </c>
       <c r="D3" s="3">
         <v>5</v>
@@ -6223,7 +5837,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -6237,13 +5851,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="D7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -6265,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C9" s="3">
         <v>4.8</v>
@@ -6279,7 +5893,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -6293,7 +5907,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -6321,7 +5935,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6335,7 +5949,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6349,13 +5963,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6363,10 +5977,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -6389,21 +6003,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -6411,10 +6025,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -6422,10 +6036,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6444,7 +6058,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
@@ -6452,46 +6066,54 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6516,10 +6138,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6531,10 +6153,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6551,31 +6173,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>92</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3">
@@ -6583,31 +6205,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4">
@@ -6615,31 +6237,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -6647,31 +6269,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -6679,31 +6301,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
@@ -6711,31 +6333,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -6743,31 +6365,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -6775,28 +6397,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>84</v>
@@ -6807,31 +6429,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
@@ -6839,31 +6461,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12">
@@ -6871,28 +6493,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F12" s="3">
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>62</v>
@@ -6903,31 +6525,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -6935,31 +6557,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="F14" s="3">
+        <v>41</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="15">
@@ -6967,31 +6589,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -6999,31 +6621,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>180</v>
+        <v>455</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>481</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -7031,31 +6653,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>275</v>
+        <v>469</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>99</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18">
@@ -7063,31 +6685,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F18" s="3">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>294</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -7095,31 +6717,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>488</v>
+        <v>274</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20">
@@ -7127,31 +6749,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>343</v>
+        <v>479</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>51</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21">
@@ -7159,31 +6781,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W40.xlsx
+++ b/reports/devops-jobs-israel-2026-W40.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30T12:25:27</t>
+    <t xml:space="preserve">2026-10-01T13:00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -531,888 +531,924 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Principal DevOps Engineer</t>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QualityAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean (acquired by Coupa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-acquired-by-coupa-4471287704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-youcc-technologies-ltd-4472699073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4474185358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE-DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blast Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4470566478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Avon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VYBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conntour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops &amp; Tooling Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tooling-engineer-at-bluebird-aero-systems-ltd-4472133947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Cloud Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-24</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QualityAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4471287704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE-DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanox Vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VYBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conntour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Cloud Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aman Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4472141600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471984090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -1440,43 +1476,16 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1491,13 +1500,16 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1649,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1657,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1665,7 +1677,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1673,7 +1685,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="10">
@@ -1745,7 +1757,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1772,20 +1784,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1793,7 +1805,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1801,7 +1813,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1809,7 +1821,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1817,7 +1829,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1830,101 +1842,101 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>323</v>
+        <v>371</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1932,15 +1944,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>495</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1948,18 +1960,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1984,13 +1996,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2">
@@ -2001,10 +2013,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>13.2</v>
+        <v>32.7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2013,88 +2025,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>39.1</v>
+        <v>36.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.1</v>
+        <v>30.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>26.0</v>
+        <v>20.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2107,7 +2119,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2178,7 +2190,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2210,7 +2222,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2242,7 +2254,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2274,7 +2286,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -2306,7 +2318,7 @@
         <v>55</v>
       </c>
       <c r="J6" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -2338,7 +2350,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -2370,7 +2382,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -2402,7 +2414,7 @@
         <v>68</v>
       </c>
       <c r="J9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2434,7 +2446,7 @@
         <v>55</v>
       </c>
       <c r="J10" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -2466,7 +2478,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2498,7 +2510,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -2530,7 +2542,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2562,7 +2574,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -2594,7 +2606,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -2626,7 +2638,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2658,7 +2670,7 @@
         <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -2690,7 +2702,7 @@
         <v>105</v>
       </c>
       <c r="J18" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2722,7 +2734,7 @@
         <v>109</v>
       </c>
       <c r="J19" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -2754,7 +2766,7 @@
         <v>99</v>
       </c>
       <c r="J20" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2786,7 +2798,7 @@
         <v>68</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2830,7 @@
         <v>119</v>
       </c>
       <c r="J22" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -2850,7 +2862,7 @@
         <v>95</v>
       </c>
       <c r="J23" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2882,7 +2894,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2914,7 +2926,7 @@
         <v>131</v>
       </c>
       <c r="J25" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
@@ -2946,7 +2958,7 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -2978,7 +2990,7 @@
         <v>139</v>
       </c>
       <c r="J27" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -3010,7 +3022,7 @@
         <v>145</v>
       </c>
       <c r="J28" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -3042,7 +3054,7 @@
         <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
@@ -3074,7 +3086,7 @@
         <v>55</v>
       </c>
       <c r="J30" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
@@ -3106,7 +3118,7 @@
         <v>84</v>
       </c>
       <c r="J31" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -3138,7 +3150,7 @@
         <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
@@ -3170,7 +3182,7 @@
         <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -3187,7 +3199,7 @@
         <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
@@ -3197,18 +3209,18 @@
         <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>172</v>
@@ -3217,28 +3229,28 @@
         <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J35" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>172</v>
@@ -3247,7 +3259,7 @@
         <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3260,21 +3272,21 @@
         <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>37</v>
@@ -3284,27 +3296,27 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="J37" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>37</v>
@@ -3314,10 +3326,10 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J38" s="3">
         <v>2</v>
@@ -3325,10 +3337,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>172</v>
@@ -3337,34 +3349,34 @@
         <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>42</v>
@@ -3374,24 +3386,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>48</v>
@@ -3404,24 +3416,24 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>48</v>
@@ -3434,27 +3446,27 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="J42" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>202</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3467,21 +3479,21 @@
         <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>48</v>
@@ -3497,27 +3509,27 @@
         <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3527,10 +3539,10 @@
         <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J45" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
@@ -3541,10 +3553,10 @@
         <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3554,24 +3566,24 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="J46" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
@@ -3584,51 +3596,51 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="J47" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J48" s="3">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>172</v>
@@ -3637,31 +3649,31 @@
         <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="J49" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -3674,27 +3686,27 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>37</v>
@@ -3704,21 +3716,21 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="J51" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>172</v>
@@ -3734,27 +3746,27 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3764,24 +3776,24 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="J53" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3794,27 +3806,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="J54" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3824,27 +3836,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3854,10 +3866,10 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J56" s="3">
         <v>2</v>
@@ -3865,19 +3877,19 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3887,51 +3899,51 @@
         <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J58" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>52</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
@@ -3944,51 +3956,51 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>172</v>
@@ -3997,31 +4009,31 @@
         <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J61" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
@@ -4034,10 +4046,10 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="J62" s="3">
         <v>1</v>
@@ -4045,10 +4057,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>172</v>
@@ -4067,7 +4079,7 @@
         <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J63" s="3">
         <v>2</v>
@@ -4075,46 +4087,46 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>52</v>
+        <v>265</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4124,57 +4136,57 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>40</v>
+        <v>251</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>202</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="J66" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4184,10 +4196,10 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>277</v>
+        <v>75</v>
       </c>
       <c r="J67" s="3">
         <v>3</v>
@@ -4195,43 +4207,43 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>48</v>
@@ -4239,32 +4251,34 @@
       <c r="E69" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4277,31 +4291,29 @@
         <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>285</v>
-      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
@@ -4309,10 +4321,10 @@
         <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4320,7 +4332,7 @@
         <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>172</v>
@@ -4339,18 +4351,18 @@
         <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="J72" s="3">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>172</v>
@@ -4369,18 +4381,18 @@
         <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="J73" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>96</v>
+        <v>291</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>172</v>
@@ -4396,10 +4408,10 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J74" s="3">
         <v>2</v>
@@ -4407,16 +4419,16 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>42</v>
@@ -4426,27 +4438,27 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>42</v>
@@ -4456,21 +4468,21 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J76" s="3">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>175</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>172</v>
@@ -4486,13 +4498,13 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="J77" s="3">
-        <v>85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -4500,7 +4512,7 @@
         <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>172</v>
@@ -4522,7 +4534,7 @@
         <v>91</v>
       </c>
       <c r="J78" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
@@ -4552,7 +4564,7 @@
         <v>40</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4582,7 +4594,7 @@
         <v>75</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -4590,10 +4602,10 @@
         <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>48</v>
@@ -4612,7 +4624,7 @@
         <v>91</v>
       </c>
       <c r="J81" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82">
@@ -4620,13 +4632,13 @@
         <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>42</v>
@@ -4636,27 +4648,27 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>238</v>
+        <v>316</v>
       </c>
       <c r="J82" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>315</v>
+        <v>52</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>42</v>
@@ -4666,54 +4678,54 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="J83" s="3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>52</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>48</v>
@@ -4722,90 +4734,90 @@
         <v>37</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>84</v>
       </c>
       <c r="J85" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>277</v>
+        <v>40</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>171</v>
+        <v>317</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>48</v>
@@ -4818,13 +4830,13 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>333</v>
+        <v>194</v>
       </c>
       <c r="J88" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4832,13 +4844,13 @@
         <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>171</v>
+        <v>335</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>42</v>
@@ -4848,10 +4860,10 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -4859,13 +4871,13 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>175</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>48</v>
@@ -4881,18 +4893,18 @@
         <v>338</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>172</v>
@@ -4911,7 +4923,7 @@
         <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="J91" s="3">
         <v>1</v>
@@ -4925,53 +4937,53 @@
         <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>194</v>
+        <v>344</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J93" s="3">
         <v>2</v>
@@ -4979,16 +4991,16 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>349</v>
+        <v>199</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>202</v>
+        <v>48</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -4998,27 +5010,27 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>326</v>
+        <v>217</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>42</v>
@@ -5028,27 +5040,27 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="J95" s="3">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>172</v>
+        <v>355</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -5058,40 +5070,40 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="J96" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>171</v>
+        <v>358</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>277</v>
+        <v>75</v>
       </c>
       <c r="J97" s="3">
         <v>3</v>
@@ -5099,10 +5111,10 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>171</v>
+        <v>361</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>172</v>
@@ -5111,34 +5123,34 @@
         <v>48</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>277</v>
+        <v>194</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>359</v>
+        <v>231</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>360</v>
+        <v>172</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>361</v>
+        <v>48</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>37</v>
@@ -5148,27 +5160,27 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>42</v>
@@ -5178,17 +5190,47 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J101" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J101"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5289,6 +5331,7 @@
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5296,9 +5339,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="55" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5330,13 +5373,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5344,18 +5387,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5363,18 +5406,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5382,18 +5425,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>334</v>
+        <v>170</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5401,18 +5444,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>335</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>348</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5420,18 +5463,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>350</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>359</v>
+        <v>284</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5439,18 +5482,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5458,11 +5501,68 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>365</v>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5471,6 +5571,9 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5484,15 +5587,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3">
         <v>24</v>
@@ -5500,7 +5603,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B3" s="3">
         <v>23</v>
@@ -5508,7 +5611,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -5516,7 +5619,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3">
         <v>21</v>
@@ -5532,7 +5635,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5540,7 +5643,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5548,7 +5651,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5556,7 +5659,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5564,7 +5667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5572,7 +5675,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -5580,7 +5683,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -5588,7 +5691,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5596,7 +5699,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5604,7 +5707,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5626,15 +5729,15 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5663,15 +5766,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5679,7 +5782,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5687,7 +5790,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5695,7 +5798,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -5711,7 +5814,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5727,7 +5830,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5735,15 +5838,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5764,16 +5867,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
@@ -5851,13 +5954,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C7" s="3">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="D7" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -5879,13 +5982,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="C9" s="3">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5893,13 +5996,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5907,7 +6010,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -5935,7 +6038,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5949,7 +6052,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6003,21 +6106,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3">
@@ -6025,10 +6128,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -6039,7 +6142,7 @@
         <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6058,7 +6161,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
@@ -6066,20 +6169,20 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6087,7 +6190,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6095,26 +6198,18 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6125,7 +6220,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -6138,10 +6233,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6153,10 +6248,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6173,31 +6268,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
@@ -6205,31 +6300,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
@@ -6237,28 +6332,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>91</v>
@@ -6269,16 +6364,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>411</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -6290,10 +6385,10 @@
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>91</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
@@ -6301,31 +6396,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F6" s="3">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F6" s="3">
-        <v>80</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>272</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
@@ -6333,31 +6428,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F7" s="3">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>91</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
@@ -6365,31 +6460,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3">
+        <v>74</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F8" s="3">
-        <v>68</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
@@ -6397,31 +6492,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="3">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F9" s="3">
-        <v>61</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>432</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -6429,31 +6524,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F10" s="3">
+        <v>68</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>437</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -6461,31 +6556,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="F11" s="3">
+        <v>61</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F11" s="3">
-        <v>47</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>443</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -6493,31 +6588,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F12" s="3">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="F12" s="3">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>62</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
@@ -6525,31 +6620,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>186</v>
+        <v>344</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>128</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -6557,31 +6652,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F14" s="3">
-        <v>41</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -6589,31 +6684,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>463</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>174</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -6621,31 +6716,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>455</v>
+        <v>183</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F16" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
@@ -6653,31 +6748,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F17" s="3">
+        <v>41</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F17" s="3">
-        <v>36</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>472</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -6685,19 +6780,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>260</v>
+        <v>471</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>472</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>473</v>
@@ -6709,7 +6804,7 @@
         <v>474</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>91</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19">
@@ -6717,31 +6812,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>274</v>
+        <v>477</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>275</v>
+        <v>466</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>277</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20">
@@ -6749,31 +6844,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>318</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21">
@@ -6781,28 +6876,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>486</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>51</v>

--- a/reports/devops-jobs-israel-2026-W40.xlsx
+++ b/reports/devops-jobs-israel-2026-W40.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01T13:00:35</t>
+    <t xml:space="preserve">2026-10-02T12:21:53</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">R&amp;D Director of Engineering</t>
+    <t xml:space="preserve">R&amp;D Director</t>
   </si>
   <si>
     <t xml:space="preserve">AWS, Azure, GCP, Security</t>
@@ -531,15 +531,21 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Echo</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
   </si>
   <si>
@@ -606,6 +612,21 @@
     <t xml:space="preserve">2026-10-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transmit Security</t>
   </si>
   <si>
@@ -615,6 +636,24 @@
     <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tonkean (acquired by Coupa)</t>
   </si>
   <si>
@@ -642,7 +681,7 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-03</t>
+    <t xml:space="preserve">2026-10-02</t>
   </si>
   <si>
     <t xml:space="preserve">Frame Security</t>
@@ -660,9 +699,6 @@
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
   </si>
   <si>
@@ -678,54 +714,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
   </si>
   <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
-  </si>
-  <si>
     <t xml:space="preserve">Claroty</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
   </si>
   <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-youcc-technologies-ltd-4472699073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4474185358</t>
   </si>
   <si>
@@ -819,9 +834,6 @@
     <t xml:space="preserve">DevOps Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
   </si>
   <si>
@@ -843,16 +855,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
   </si>
   <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4470860757</t>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
   </si>
   <si>
     <t xml:space="preserve">Unframe</t>
@@ -864,13 +888,103 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops &amp; Tooling Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tooling-engineer-at-bluebird-aero-systems-ltd-4472133947</t>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
   </si>
   <si>
     <t xml:space="preserve">ThetaRay</t>
@@ -882,76 +996,97 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
   </si>
   <si>
     <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
@@ -960,543 +1095,372 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Cloud Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -1506,10 +1470,7 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1661,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -1669,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1677,7 +1638,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -1685,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="10">
@@ -1757,7 +1718,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1784,36 +1745,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1821,7 +1782,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1829,7 +1790,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1842,93 +1803,93 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1936,42 +1897,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>495</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1996,13 +1957,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
@@ -2013,10 +1974,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>32.7</v>
+        <v>14.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2025,88 +1986,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>9.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.0</v>
+        <v>34.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.9</v>
+        <v>14.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2190,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2222,7 +2183,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2254,7 +2215,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2286,7 +2247,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -2318,7 +2279,7 @@
         <v>55</v>
       </c>
       <c r="J6" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -2350,7 +2311,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -2382,7 +2343,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -2414,7 +2375,7 @@
         <v>68</v>
       </c>
       <c r="J9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2446,7 +2407,7 @@
         <v>55</v>
       </c>
       <c r="J10" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -2478,7 +2439,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2510,7 +2471,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -2542,7 +2503,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -2574,7 +2535,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -2606,7 +2567,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -2638,7 +2599,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2670,7 +2631,7 @@
         <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -2702,7 +2663,7 @@
         <v>105</v>
       </c>
       <c r="J18" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2734,7 +2695,7 @@
         <v>109</v>
       </c>
       <c r="J19" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -2766,7 +2727,7 @@
         <v>99</v>
       </c>
       <c r="J20" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2798,7 +2759,7 @@
         <v>68</v>
       </c>
       <c r="J21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -2830,7 +2791,7 @@
         <v>119</v>
       </c>
       <c r="J22" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -2862,7 +2823,7 @@
         <v>95</v>
       </c>
       <c r="J23" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
@@ -2894,7 +2855,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2926,7 +2887,7 @@
         <v>131</v>
       </c>
       <c r="J25" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -2958,7 +2919,7 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -2990,7 +2951,7 @@
         <v>139</v>
       </c>
       <c r="J27" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -3022,7 +2983,7 @@
         <v>145</v>
       </c>
       <c r="J28" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -3054,7 +3015,7 @@
         <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -3086,7 +3047,7 @@
         <v>55</v>
       </c>
       <c r="J30" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -3118,7 +3079,7 @@
         <v>84</v>
       </c>
       <c r="J31" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -3150,7 +3111,7 @@
         <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -3182,111 +3143,111 @@
         <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D34" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="J34" s="3">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="J35" s="3">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J36" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>37</v>
@@ -3296,27 +3257,27 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>37</v>
@@ -3329,27 +3290,27 @@
         <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J38" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3359,10 +3320,10 @@
         <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="J39" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -3370,13 +3331,13 @@
         <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>42</v>
@@ -3386,27 +3347,27 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>42</v>
@@ -3416,18 +3377,18 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="J41" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>198</v>
@@ -3436,7 +3397,7 @@
         <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>42</v>
@@ -3446,30 +3407,30 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3479,27 +3440,27 @@
         <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="J43" s="3">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3509,24 +3470,24 @@
         <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="J44" s="3">
-        <v>90</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>42</v>
@@ -3539,15 +3500,15 @@
         <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="J45" s="3">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>211</v>
@@ -3556,127 +3517,127 @@
         <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>215</v>
+        <v>40</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
@@ -3686,30 +3647,30 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J50" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
@@ -3719,21 +3680,21 @@
         <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
@@ -3749,24 +3710,24 @@
         <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>233</v>
+        <v>164</v>
       </c>
       <c r="J52" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3779,21 +3740,21 @@
         <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3806,27 +3767,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>241</v>
+        <v>142</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3836,27 +3797,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3866,10 +3827,10 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>40</v>
+        <v>227</v>
       </c>
       <c r="J56" s="3">
         <v>2</v>
@@ -3877,19 +3838,19 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3902,48 +3863,48 @@
         <v>75</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
@@ -3956,24 +3917,24 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J59" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -3986,54 +3947,54 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>40</v>
+        <v>256</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="C61" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
@@ -4049,10 +4010,10 @@
         <v>262</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>215</v>
+        <v>40</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4060,10 +4021,10 @@
         <v>263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
@@ -4076,18 +4037,18 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>265</v>
+        <v>52</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>266</v>
@@ -4096,10 +4057,10 @@
         <v>212</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -4109,24 +4070,24 @@
         <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="J64" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4136,57 +4097,57 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>208</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>170</v>
+        <v>273</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4199,27 +4160,27 @@
         <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4232,28 +4193,26 @@
         <v>75</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>172</v>
+        <v>279</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>279</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
@@ -4261,24 +4220,24 @@
         <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4288,27 +4247,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>194</v>
+        <v>75</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>285</v>
+        <v>59</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
@@ -4318,32 +4277,34 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
@@ -4351,21 +4312,21 @@
         <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="J72" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>96</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>289</v>
+        <v>177</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>48</v>
@@ -4381,21 +4342,21 @@
         <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
@@ -4408,27 +4369,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="C75" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>241</v>
+        <v>48</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>42</v>
@@ -4438,27 +4399,27 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>297</v>
+        <v>40</v>
       </c>
       <c r="J75" s="3">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>48</v>
+        <v>246</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>42</v>
@@ -4468,24 +4429,24 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J76" s="3">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
@@ -4498,13 +4459,13 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78">
@@ -4512,16 +4473,16 @@
         <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -4531,21 +4492,21 @@
         <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="J78" s="3">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>236</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>48</v>
@@ -4561,24 +4522,24 @@
         <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>309</v>
+        <v>171</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4588,10 +4549,10 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J80" s="3">
         <v>3</v>
@@ -4599,19 +4560,19 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D81" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
@@ -4621,24 +4582,24 @@
         <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="J81" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>241</v>
+        <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>42</v>
@@ -4648,32 +4609,34 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>316</v>
+        <v>75</v>
       </c>
       <c r="J82" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
@@ -4681,10 +4644,10 @@
         <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -4695,13 +4658,13 @@
         <v>320</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4711,116 +4674,114 @@
         <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="J84" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="I85" s="3" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="J85" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>48</v>
+        <v>246</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4830,27 +4791,27 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>241</v>
+        <v>48</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>42</v>
@@ -4860,24 +4821,24 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="C90" s="3" t="s">
-        <v>172</v>
+        <v>338</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>48</v>
@@ -4890,13 +4851,13 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>339</v>
+        <v>40</v>
       </c>
       <c r="J90" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4904,10 +4865,10 @@
         <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>48</v>
@@ -4923,10 +4884,10 @@
         <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4934,10 +4895,10 @@
         <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>343</v>
+        <v>177</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>344</v>
+        <v>171</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
@@ -4950,24 +4911,24 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>40</v>
+        <v>256</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>48</v>
@@ -4980,24 +4941,24 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>48</v>
@@ -5010,57 +4971,57 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>217</v>
+        <v>310</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>172</v>
+        <v>351</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="J95" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>308</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>355</v>
+        <v>212</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -5070,54 +5031,54 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>358</v>
+        <v>229</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J97" s="3">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>361</v>
+        <v>236</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>48</v>
@@ -5130,107 +5091,17 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J99" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="J100" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J101" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J98"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5329,9 +5200,6 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5339,8 +5207,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5373,13 +5241,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5387,18 +5255,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5406,174 +5274,14 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>362</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
-    <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5587,15 +5295,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3">
         <v>24</v>
@@ -5603,7 +5311,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B3" s="3">
         <v>23</v>
@@ -5611,7 +5319,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -5619,7 +5327,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3">
         <v>21</v>
@@ -5635,7 +5343,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5643,7 +5351,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5651,7 +5359,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5659,7 +5367,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5667,7 +5375,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5675,7 +5383,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -5683,7 +5391,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -5691,7 +5399,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5699,7 +5407,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5707,7 +5415,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5720,7 +5428,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5729,15 +5437,15 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5790,7 +5498,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5798,15 +5506,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5814,7 +5522,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5822,7 +5530,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5830,7 +5538,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5838,7 +5546,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5860,23 +5568,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5954,13 +5662,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C7" s="3">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5996,7 +5704,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -6010,13 +5718,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6024,13 +5732,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="C12" s="3">
-        <v>3.0</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6038,7 +5746,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6052,13 +5760,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>330</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6066,10 +5774,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -6080,13 +5788,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6106,21 +5814,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3">
@@ -6128,10 +5836,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
@@ -6139,10 +5847,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -6161,7 +5869,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -6169,7 +5877,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -6177,12 +5885,12 @@
         <v>142</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6190,7 +5898,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6206,7 +5914,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6220,7 +5928,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -6233,10 +5941,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6248,10 +5956,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6268,31 +5976,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -6300,31 +6008,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4">
@@ -6332,28 +6040,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>172</v>
+        <v>401</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>91</v>
@@ -6364,31 +6072,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>231</v>
+        <v>406</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>215</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -6396,31 +6104,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F6" s="3">
         <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
@@ -6428,31 +6136,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F7" s="3">
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8">
@@ -6460,31 +6168,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
         <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
@@ -6492,28 +6200,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="F9" s="3">
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>91</v>
@@ -6524,31 +6232,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F10" s="3">
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -6556,28 +6264,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F11" s="3">
         <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>84</v>
@@ -6588,31 +6296,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>199</v>
+        <v>338</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>215</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13">
@@ -6620,31 +6328,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>344</v>
+        <v>239</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>448</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -6652,31 +6360,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>450</v>
+        <v>278</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>451</v>
+        <v>279</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>454</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -6684,31 +6392,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>229</v>
+        <v>451</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>457</v>
+        <v>389</v>
       </c>
       <c r="F15" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>62</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16">
@@ -6716,31 +6424,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>183</v>
+        <v>279</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -6748,31 +6456,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>466</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="F17" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>40</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18">
@@ -6780,31 +6488,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>471</v>
+        <v>261</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>472</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>475</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -6812,31 +6520,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>466</v>
+        <v>185</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>91</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20">
@@ -6844,31 +6552,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>481</v>
+        <v>284</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>484</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -6876,31 +6584,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>486</v>
+        <v>239</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>51</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W40.xlsx
+++ b/reports/devops-jobs-israel-2026-W40.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="494">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02T12:21:53</t>
+    <t xml:space="preserve">2026-10-04T12:13:53</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -159,1161 +159,1164 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4983402101?gh_jid=4983402101</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;D Director</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8235896&amp;gh_jid=8235896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevSecOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nym-4473896883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QualityAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean (acquired by Coupa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-acquired-by-coupa-4471287704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bynet-data-communications-4473467922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4474185358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE-DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polytex Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Avon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VYBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conntour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;D Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8235896&amp;gh_jid=8235896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QualityAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualityai-4472498310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean (acquired by Coupa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-acquired-by-coupa-4471287704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4474185358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE-DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pipl-4472443997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4473088532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4472436717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blast Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4470566478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VYBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conntour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-conntour-4470835721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4472445519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-senior-devops-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4470816696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4472450722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-4471278258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4471784293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-at-sqlink-group-4470847671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1455,10 +1458,10 @@
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud (any)</t>
@@ -1622,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1638,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1646,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>905</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10">
@@ -1718,7 +1721,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1726,7 +1729,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1766,18 +1769,18 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1790,7 +1793,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1809,23 +1812,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -1836,7 +1839,7 @@
         <v>369</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1844,20 +1847,20 @@
         <v>372</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -1865,7 +1868,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -1881,7 +1884,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1889,7 +1892,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1913,7 +1916,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
@@ -1921,7 +1924,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1929,7 +1932,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1957,13 +1960,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2">
@@ -1971,13 +1974,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1986,88 +1989,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.3</v>
+        <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.8</v>
+        <v>35.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.2</v>
+        <v>18.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.4</v>
+        <v>25.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2078,8 +2081,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2151,7 +2154,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2186,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2215,7 +2218,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2232,7 +2235,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>49</v>
@@ -2247,7 +2250,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2267,30 +2270,30 @@
         <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="3">
         <v>54</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="3">
-        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
@@ -2299,7 +2302,7 @@
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
@@ -2308,21 +2311,21 @@
         <v>57</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -2331,36 +2334,36 @@
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>66</v>
@@ -2372,21 +2375,21 @@
         <v>67</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>17</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>48</v>
@@ -2395,19 +2398,19 @@
         <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="J10" s="3">
-        <v>52</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2415,16 +2418,16 @@
         <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>73</v>
@@ -2439,7 +2442,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -2447,10 +2450,10 @@
         <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>48</v>
@@ -2459,27 +2462,27 @@
         <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
@@ -2491,27 +2494,27 @@
         <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J13" s="3">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>48</v>
@@ -2535,7 +2538,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2543,7 +2546,7 @@
         <v>88</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
@@ -2567,7 +2570,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -2575,7 +2578,7 @@
         <v>92</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>48</v>
@@ -2599,7 +2602,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="3">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -2607,10 +2610,10 @@
         <v>96</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>48</v>
@@ -2619,30 +2622,30 @@
         <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>48</v>
@@ -2663,7 +2666,7 @@
         <v>105</v>
       </c>
       <c r="J18" s="3">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -2671,16 +2674,16 @@
         <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>107</v>
@@ -2692,21 +2695,21 @@
         <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J19" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
@@ -2715,51 +2718,51 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="J20" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="J21" s="3">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -2767,10 +2770,10 @@
         <v>116</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>48</v>
@@ -2779,19 +2782,19 @@
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="J22" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -2799,10 +2802,10 @@
         <v>120</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>48</v>
@@ -2820,21 +2823,21 @@
         <v>123</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="J23" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>48</v>
@@ -2843,27 +2846,27 @@
         <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>48</v>
@@ -2872,30 +2875,30 @@
         <v>48</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J25" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>48</v>
@@ -2904,97 +2907,97 @@
         <v>48</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="J26" s="3">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J28" s="3">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>48</v>
@@ -3003,71 +3006,71 @@
         <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="J29" s="3">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="J30" s="3">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
@@ -3076,18 +3079,18 @@
         <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>48</v>
@@ -3099,62 +3102,60 @@
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>167</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>48</v>
@@ -3170,10 +3171,10 @@
         <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -3184,7 +3185,7 @@
         <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>48</v>
@@ -3200,84 +3201,84 @@
         <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J35" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="J36" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="J37" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>37</v>
@@ -3287,13 +3288,13 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3301,10 +3302,10 @@
         <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
@@ -3317,24 +3318,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>48</v>
@@ -3350,10 +3351,10 @@
         <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J40" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -3367,7 +3368,7 @@
         <v>194</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>42</v>
@@ -3383,7 +3384,7 @@
         <v>196</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -3410,27 +3411,27 @@
         <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J42" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3440,27 +3441,27 @@
         <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="J43" s="3">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3470,51 +3471,51 @@
         <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="J44" s="3">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="J45" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>48</v>
@@ -3527,24 +3528,24 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
@@ -3557,40 +3558,40 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J47" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3598,13 +3599,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
@@ -3617,24 +3618,24 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J49" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>200</v>
@@ -3647,24 +3648,24 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -3677,13 +3678,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>196</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3691,10 +3692,10 @@
         <v>173</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
@@ -3707,24 +3708,24 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J52" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>48</v>
@@ -3737,24 +3738,24 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3767,54 +3768,54 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="J54" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>48</v>
@@ -3827,13 +3828,13 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -3841,13 +3842,13 @@
         <v>173</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>246</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3857,13 +3858,13 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -3871,13 +3872,13 @@
         <v>173</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3887,10 +3888,10 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="J58" s="3">
         <v>3</v>
@@ -3898,29 +3899,29 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="J59" s="3">
         <v>4</v>
@@ -3928,43 +3929,43 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>48</v>
@@ -3977,57 +3978,57 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="J61" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
@@ -4037,87 +4038,87 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>52</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4127,87 +4128,87 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="J66" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="J67" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>279</v>
+        <v>209</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>42</v>
@@ -4217,54 +4218,54 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="J70" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>48</v>
@@ -4277,56 +4278,54 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J71" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>190</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>287</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="J72" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>48</v>
@@ -4339,24 +4338,24 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="J73" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>96</v>
+        <v>286</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
@@ -4369,24 +4368,24 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>48</v>
@@ -4399,163 +4398,163 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>246</v>
+        <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>299</v>
+        <v>87</v>
       </c>
       <c r="J76" s="3">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>303</v>
+        <v>40</v>
       </c>
       <c r="J77" s="3">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>236</v>
+        <v>301</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>171</v>
+        <v>302</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="J79" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>46</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -4563,13 +4562,13 @@
         <v>306</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>37</v>
@@ -4579,24 +4578,24 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>48</v>
@@ -4609,75 +4608,75 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3">
         <v>84</v>
-      </c>
-      <c r="J83" s="3">
-        <v>32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>136</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -4685,13 +4684,13 @@
         <v>173</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
@@ -4701,27 +4700,27 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>196</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>37</v>
@@ -4731,24 +4730,24 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>48</v>
@@ -4761,27 +4760,27 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>196</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4791,24 +4790,24 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>196</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>48</v>
@@ -4821,10 +4820,10 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>256</v>
+        <v>40</v>
       </c>
       <c r="J89" s="3">
         <v>5</v>
@@ -4832,13 +4831,13 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>338</v>
+        <v>168</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>48</v>
@@ -4851,24 +4850,24 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>48</v>
@@ -4881,27 +4880,27 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>342</v>
+        <v>52</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>177</v>
+        <v>338</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>42</v>
@@ -4911,54 +4910,54 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>348</v>
+        <v>252</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>48</v>
@@ -4971,27 +4970,27 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>40</v>
+        <v>254</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>351</v>
+        <v>168</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>37</v>
@@ -5001,24 +5000,24 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>48</v>
@@ -5031,24 +5030,24 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>48</v>
@@ -5061,24 +5060,24 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J97" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>48</v>
@@ -5091,17 +5090,47 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J98" s="3">
-        <v>22</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J99" s="3">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5200,6 +5229,7 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5207,8 +5237,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5241,13 +5271,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5255,18 +5285,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>279</v>
+        <v>209</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5274,14 +5304,114 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>280</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5295,26 +5425,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -5322,7 +5452,7 @@
         <v>362</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -5330,12 +5460,12 @@
         <v>363</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5354,7 +5484,7 @@
         <v>365</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -5370,7 +5500,7 @@
         <v>367</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -5428,7 +5558,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5442,15 +5572,15 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5458,23 +5588,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5482,7 +5612,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5490,7 +5620,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5498,15 +5628,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5514,7 +5644,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5522,7 +5652,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5530,7 +5660,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5538,7 +5668,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5546,7 +5676,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5554,7 +5684,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5568,7 +5698,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
@@ -5592,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3">
         <v>23.8</v>
@@ -5606,7 +5736,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3">
         <v>18.6</v>
@@ -5620,7 +5750,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3">
         <v>13.4</v>
@@ -5634,10 +5764,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5648,10 +5778,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
-        <v>10.1</v>
+        <v>7.1</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -5662,13 +5792,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5676,13 +5806,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5690,13 +5820,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5704,7 +5834,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5718,7 +5848,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3">
         <v>3.0</v>
@@ -5732,7 +5862,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5746,13 +5876,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5760,10 +5890,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -5774,13 +5904,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5788,7 +5918,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5836,7 +5966,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>381</v>
@@ -5847,7 +5977,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>382</v>
@@ -5882,31 +6012,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5914,10 +6044,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6014,7 +6144,7 @@
         <v>394</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>395</v>
@@ -6064,7 +6194,7 @@
         <v>404</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -6075,10 +6205,10 @@
         <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>389</v>
@@ -6087,16 +6217,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -6104,13 +6234,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>389</v>
@@ -6119,16 +6249,16 @@
         <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
@@ -6136,13 +6266,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>389</v>
@@ -6151,16 +6281,16 @@
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="8">
@@ -6174,7 +6304,7 @@
         <v>418</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>338</v>
+        <v>231</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>402</v>
@@ -6192,7 +6322,7 @@
         <v>420</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -6224,7 +6354,7 @@
         <v>425</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -6256,7 +6386,7 @@
         <v>430</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>179</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -6264,31 +6394,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F11" s="3">
         <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -6296,31 +6426,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>418</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>338</v>
+        <v>231</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13">
@@ -6328,31 +6458,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -6360,28 +6490,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F14" s="3">
         <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>40</v>
@@ -6392,13 +6522,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>389</v>
@@ -6407,16 +6537,16 @@
         <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">
@@ -6424,13 +6554,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>402</v>
@@ -6439,16 +6569,16 @@
         <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -6456,13 +6586,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>389</v>
@@ -6471,16 +6601,16 @@
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18">
@@ -6488,13 +6618,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>389</v>
@@ -6503,16 +6633,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -6520,31 +6650,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20">
@@ -6552,13 +6682,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>389</v>
@@ -6567,16 +6697,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>51</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21">
@@ -6584,13 +6714,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>389</v>
@@ -6599,16 +6729,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
